--- a/figures/timeline.xlsx
+++ b/figures/timeline.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qizhg/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qizhg-mba/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD137C41-A6E3-7C4F-A9C9-9D94FF631624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58436220-BEAA-5F4E-A7C7-665D52596FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{E1123A9C-C35D-8449-8A9E-32358150E071}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{E1123A9C-C35D-8449-8A9E-32358150E071}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1 (2)" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1 (2)" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -35,73 +34,46 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="20">
-  <si>
-    <t>Thrusts and Roles</t>
-  </si>
-  <si>
-    <t>Year 1</t>
-  </si>
-  <si>
-    <t>Year 3</t>
-  </si>
-  <si>
-    <t>Year 2</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>o</t>
-  </si>
-  <si>
-    <t>1 - PLM bandit policy with historical interaction [YZ]</t>
-  </si>
-  <si>
-    <t>1 - Mixing PLM and standard bandit policies [QZ, YZ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - Foundation models for textual subgoal generation [QZ] </t>
-  </si>
-  <si>
-    <t>3a -  Centralized multi-agent communication [QZ, YZ]</t>
-  </si>
-  <si>
-    <t>3b - Decentralized multi-agent communication [YZ]</t>
-  </si>
-  <si>
-    <t>1b [QZ, YZ]</t>
-  </si>
-  <si>
-    <t>1a [YZ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 [QZ] </t>
-  </si>
-  <si>
-    <t>3a [QZ, YZ]</t>
-  </si>
-  <si>
-    <t>3b [YZ]</t>
-  </si>
-  <si>
-    <t>Thrusts [Roles]</t>
-  </si>
-  <si>
-    <t>Y1</t>
-  </si>
-  <si>
-    <t>Y2</t>
-  </si>
-  <si>
-    <t>Y3</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>Setup</t>
+  </si>
+  <si>
+    <t>Theory</t>
+  </si>
+  <si>
+    <t>Unification</t>
+  </si>
+  <si>
+    <t>Code &amp; Paper</t>
+  </si>
+  <si>
+    <t>Submission</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Baselines </t>
+  </si>
+  <si>
+    <t>Algorithms</t>
+  </si>
+  <si>
+    <t>Views 1+2</t>
+  </si>
+  <si>
+    <t>View 1</t>
+  </si>
+  <si>
+    <t>View 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -110,28 +82,43 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Palatino"/>
-      <family val="1"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Palatino"/>
-      <family val="1"/>
+      <name val="Latin mordern"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Latin mordern"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Latin mordern"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9948118533890809E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -154,28 +141,83 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -196,9 +238,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -236,7 +278,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -342,7 +384,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -484,243 +526,196 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5918706-CC5D-184A-AFEF-3906D7F6E80F}">
-  <dimension ref="B2:H7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A85EDA-A2EA-164D-91CD-D7A3A6058FAC}">
+  <dimension ref="B2:P7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="4" style="1" customWidth="1"/>
-    <col min="2" max="2" width="48.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="4.33203125" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="1"/>
+    <col min="2" max="2" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="2" customWidth="1"/>
+    <col min="4" max="6" width="3.1640625" style="2" customWidth="1"/>
+    <col min="7" max="14" width="3.33203125" style="2" customWidth="1"/>
+    <col min="15" max="16" width="4.5" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="2:16">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="3">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2" s="3">
+        <v>5</v>
+      </c>
+      <c r="H2" s="3">
+        <v>6</v>
+      </c>
+      <c r="I2" s="3">
+        <v>7</v>
+      </c>
+      <c r="J2" s="3">
+        <v>8</v>
+      </c>
+      <c r="K2" s="3">
+        <v>9</v>
+      </c>
+      <c r="L2" s="3">
+        <v>10</v>
+      </c>
+      <c r="M2" s="3">
+        <v>11</v>
+      </c>
+      <c r="N2" s="3">
+        <v>12</v>
+      </c>
+      <c r="O2" s="3">
+        <v>13</v>
+      </c>
+      <c r="P2" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" ht="17" customHeight="1">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6" t="s">
+      <c r="C3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="12"/>
+    </row>
+    <row r="4" spans="2:16" ht="17" customHeight="1">
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="12"/>
+    </row>
+    <row r="5" spans="2:16" ht="17" customHeight="1">
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="12"/>
+    </row>
+    <row r="6" spans="2:16" ht="17" customHeight="1">
+      <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="6"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="12"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
+    <row r="7" spans="2:16" ht="17" customHeight="1">
+      <c r="B7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="P7" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
+  <mergeCells count="12">
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="D3:P3"/>
+    <mergeCell ref="K4:P4"/>
+    <mergeCell ref="K5:P5"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="C7:N7"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:J4"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A85EDA-A2EA-164D-91CD-D7A3A6058FAC}">
-  <dimension ref="B2:H7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="4" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="2.5" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="6"/>
-    </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/figures/timeline.xlsx
+++ b/figures/timeline.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qizhg-mba/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qizhg-mba/ara_spring2026/figures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58436220-BEAA-5F4E-A7C7-665D52596FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F419D7E6-887F-2B47-8A6F-33A8AAA7E635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{E1123A9C-C35D-8449-8A9E-32358150E071}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{E1123A9C-C35D-8449-8A9E-32358150E071}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1 (2)" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1 (3)" sheetId="4" r:id="rId1"/>
+    <sheet name="Sheet1 (2)" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="11">
   <si>
     <t>M1</t>
   </si>
@@ -199,6 +200,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -207,9 +211,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -533,6 +534,194 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4D9007F-E049-B444-9166-71E8FD51480A}">
+  <dimension ref="B2:P7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="4" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="2" customWidth="1"/>
+    <col min="4" max="6" width="3.1640625" style="2" customWidth="1"/>
+    <col min="7" max="14" width="3.33203125" style="2" customWidth="1"/>
+    <col min="15" max="16" width="4.5" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:16">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2" s="3">
+        <v>5</v>
+      </c>
+      <c r="H2" s="3">
+        <v>6</v>
+      </c>
+      <c r="I2" s="3">
+        <v>7</v>
+      </c>
+      <c r="J2" s="3">
+        <v>8</v>
+      </c>
+      <c r="K2" s="3">
+        <v>9</v>
+      </c>
+      <c r="L2" s="3">
+        <v>10</v>
+      </c>
+      <c r="M2" s="3">
+        <v>11</v>
+      </c>
+      <c r="N2" s="3">
+        <v>12</v>
+      </c>
+      <c r="O2" s="3">
+        <v>13</v>
+      </c>
+      <c r="P2" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" ht="17" customHeight="1">
+      <c r="B3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="12"/>
+    </row>
+    <row r="4" spans="2:16" ht="17" customHeight="1">
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="12"/>
+    </row>
+    <row r="5" spans="2:16" ht="17" customHeight="1">
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="12"/>
+    </row>
+    <row r="6" spans="2:16" ht="17" customHeight="1">
+      <c r="B6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="12"/>
+    </row>
+    <row r="7" spans="2:16" ht="17" customHeight="1">
+      <c r="B7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="P7" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="C7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="D3:P3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="K4:P4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="K5:P5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A85EDA-A2EA-164D-91CD-D7A3A6058FAC}">
   <dimension ref="B2:P7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -617,17 +806,17 @@
         <v>9</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="6" t="s">
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="9"/>
       <c r="K4" s="10"/>
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
@@ -635,22 +824,22 @@
       <c r="O4" s="11"/>
       <c r="P4" s="12"/>
     </row>
-    <row r="5" spans="2:16" ht="17" customHeight="1">
+    <row r="5" spans="2:16">
       <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="6" t="s">
+      <c r="E5" s="8"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="9"/>
       <c r="K5" s="10"/>
       <c r="L5" s="11"/>
       <c r="M5" s="11"/>
@@ -658,7 +847,7 @@
       <c r="O5" s="11"/>
       <c r="P5" s="12"/>
     </row>
-    <row r="6" spans="2:16" ht="17" customHeight="1">
+    <row r="6" spans="2:16">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -670,17 +859,17 @@
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
       <c r="J6" s="12"/>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="9"/>
       <c r="O6" s="10"/>
       <c r="P6" s="12"/>
     </row>
-    <row r="7" spans="2:16" ht="17" customHeight="1">
-      <c r="B7" s="9" t="s">
+    <row r="7" spans="2:16" ht="32">
+      <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="10"/>
@@ -695,10 +884,10 @@
       <c r="L7" s="11"/>
       <c r="M7" s="11"/>
       <c r="N7" s="12"/>
-      <c r="O7" s="6" t="s">
+      <c r="O7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="P7" s="8"/>
+      <c r="P7" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="12">
